--- a/files/臻畅-2026Q3-项目汇总-20261018_v2含S56价格.xlsx
+++ b/files/臻畅-2026Q3-项目汇总-20261018_v2含S56价格.xlsx
@@ -1579,7 +1579,7 @@
       </c>
       <c r="K8" s="19" t="inlineStr">
         <is>
-          <t>内部定点 9/16；价格 10/18 已出：13 件定点单价合计 15.9771 未税 / 18.0542 含税，平均毛利率 18.9%；首单 PO4500127228（12,040 件）回填 ¥23,239.66，待客户签认</t>
+          <t>内部定点 9/16；价格 10/18 已出：13 件按单车 16 件加权，套成本 13.9319 / 套未税 17.0695 / 套含税 19.2886（毛利率 18.4%）；首单 PO4500127228 回填 ¥23,239.66，待客户签认</t>
         </is>
       </c>
     </row>
@@ -6140,6 +6140,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41" ht="16.5" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
@@ -6163,7 +6164,7 @@
       </c>
       <c r="C42" s="26" t="inlineStr">
         <is>
-          <t>价格更新：13 件定点单价合计 15.9771 未税 / 18.0542 含税（成本 12.9632，毛利率 18.9%）；首单 PO4500127228 回填含税 ¥23,239.66</t>
+          <t>价格更新：13 件按单车 16 件加权，套成本 13.9319 / 套未税 17.0695 / 套含税 19.2886（毛利率 18.4%）；首单 PO4500127228 回填含税 ¥23,239.66。⚠️ 表单合计行 15.9771/18.0542 未乘用量</t>
         </is>
       </c>
       <c r="D42" s="26" t="inlineStr">
@@ -10280,7 +10281,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
